--- a/data/trans_orig/IP22D3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40907</t>
+          <t>40870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>46866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>38614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49072</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82183</t>
+          <t>82292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94239</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1874</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2328</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>857</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4740</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6652</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5893</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4586</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>74,56%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5471</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3933</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6261</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>62,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>20</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5135</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>20,95%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>48,9%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2526</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5842</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>851</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -1402,74 +1402,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4807</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9623</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>74,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7568</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5703</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4983</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7028</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9492</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6386</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11689</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>75,71%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>50,93%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>24</t>
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17059</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>717</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>363</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1971,74 +1971,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13459</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9789</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>64,75%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9069</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>6959</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9767</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8381</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>82,73%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>14969</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>11216</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16719</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>89,53%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>67,09%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>29</t>
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>23227</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>24877</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5495</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4796</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14434</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9153</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16869</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>82,28%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>52,18%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>96,17%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>21342</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17382</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>73,66%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>31806</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29798</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13022</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>7296</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>15,15%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>40483</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>34183</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>44487</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>83,47%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>70,48%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>44630</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>40870</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>46866</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>84,85%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38614</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49034</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>80123</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82292</t>
+          <t>73751</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94198</t>
+          <t>84883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -3222,107 +3222,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4806</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -3335,107 +3335,107 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
